--- a/Downloads/Exposure Template.xlsx
+++ b/Downloads/Exposure Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://datadriventv-my.sharepoint.com/personal/kayla_lai_ampersand_tv/Documents/Documents/Weekly Items/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://datadriventv-my.sharepoint.com/personal/kostiantyn_rymar_ampersand_tv/Documents/Automation projects/Curious-Series/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{76A2DCF1-1F12-429D-AE52-2B3BB7751F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC7C988-7D14-41ED-99F3-B513C94964A1}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{76A2DCF1-1F12-429D-AE52-2B3BB7751F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94206D09-BD05-4F0C-8E1A-3BAF4F10B3AC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A8B9BC57-1BDA-4BD5-8226-154C3D1C8245}"/>
+    <workbookView xWindow="-28920" yWindow="-3660" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A8B9BC57-1BDA-4BD5-8226-154C3D1C8245}"/>
   </bookViews>
   <sheets>
     <sheet name="Exposure Template 011426" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="219">
   <si>
     <t>Client</t>
   </si>
@@ -110,15 +110,9 @@
     <t>Band</t>
   </si>
   <si>
-    <t>WINTRUST</t>
-  </si>
-  <si>
     <t>W10</t>
   </si>
   <si>
-    <t>1000</t>
-  </si>
-  <si>
     <t>Milwaukee-Racine</t>
   </si>
   <si>
@@ -128,9 +122,6 @@
     <t>APL</t>
   </si>
   <si>
-    <t>WTSB20230H</t>
-  </si>
-  <si>
     <t>20260119</t>
   </si>
   <si>
@@ -684,6 +675,9 @@
   </si>
   <si>
     <t>1512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinent 2 </t>
   </si>
 </sst>
 </file>
@@ -1255,10 +1249,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1581,20 +1571,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" customWidth="1"/>
-    <col min="15" max="15" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
@@ -1615,7 +1605,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1669,4751 +1659,4751 @@
       </c>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>2222</v>
       </c>
       <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="K3">
+        <v>123</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
         <v>33</v>
       </c>
-      <c r="H3" t="s">
+      <c r="N3" t="s">
         <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>2222</v>
       </c>
       <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4">
+        <v>123</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
         <v>33</v>
       </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>36</v>
-      </c>
-      <c r="N4" t="s">
-        <v>39</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>2222</v>
       </c>
       <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5">
+        <v>123</v>
+      </c>
+      <c r="L5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
         <v>33</v>
       </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
       <c r="N5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>2222</v>
       </c>
       <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
+      <c r="K6">
+        <v>123</v>
       </c>
       <c r="L6" t="s">
         <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>2222</v>
       </c>
       <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
         <v>32</v>
       </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" t="s">
-        <v>35</v>
+      <c r="K7">
+        <v>123</v>
       </c>
       <c r="L7" t="s">
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>2222</v>
       </c>
       <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
+      <c r="K8">
+        <v>123</v>
       </c>
       <c r="L8" t="s">
         <v>21</v>
       </c>
       <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" t="s">
         <v>45</v>
-      </c>
-      <c r="N8" t="s">
-        <v>48</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>2222</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9">
+        <v>123</v>
+      </c>
+      <c r="L9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s">
         <v>33</v>
       </c>
-      <c r="H9" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>36</v>
-      </c>
       <c r="N9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>2222</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10">
+        <v>123</v>
+      </c>
+      <c r="L10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" t="s">
+      <c r="N10" t="s">
         <v>49</v>
-      </c>
-      <c r="K10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" t="s">
-        <v>52</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>2222</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11">
+        <v>123</v>
+      </c>
+      <c r="L11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
-      </c>
       <c r="N11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>2222</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12">
+        <v>123</v>
+      </c>
+      <c r="L12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>36</v>
-      </c>
       <c r="N12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>2222</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13">
+        <v>123</v>
+      </c>
+      <c r="L13" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" t="s">
         <v>53</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" t="s">
-        <v>56</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D14">
+        <v>2222</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
+        <v>46</v>
+      </c>
+      <c r="K14">
+        <v>123</v>
       </c>
       <c r="L14" t="s">
         <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>2222</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="K15">
+        <v>123</v>
       </c>
       <c r="L15" t="s">
         <v>21</v>
       </c>
       <c r="M15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>2222</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="K16">
+        <v>123</v>
       </c>
       <c r="L16" t="s">
         <v>21</v>
       </c>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>2222</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="K17">
+        <v>123</v>
       </c>
       <c r="L17" t="s">
         <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="Q17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>2222</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="K18">
+        <v>123</v>
       </c>
       <c r="L18" t="s">
         <v>21</v>
       </c>
       <c r="M18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="Q18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>2222</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19">
+        <v>123</v>
+      </c>
+      <c r="L19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" t="s">
         <v>33</v>
       </c>
-      <c r="H19" t="s">
-        <v>69</v>
-      </c>
-      <c r="K19" t="s">
-        <v>35</v>
-      </c>
-      <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>36</v>
-      </c>
       <c r="N19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>2222</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20">
+        <v>123</v>
+      </c>
+      <c r="L20" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" t="s">
         <v>33</v>
       </c>
-      <c r="H20" t="s">
-        <v>72</v>
-      </c>
-      <c r="K20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>36</v>
-      </c>
       <c r="N20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D21">
+        <v>2222</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21">
+        <v>123</v>
+      </c>
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" t="s">
         <v>33</v>
       </c>
-      <c r="H21" t="s">
+      <c r="N21" t="s">
         <v>72</v>
-      </c>
-      <c r="K21" t="s">
-        <v>35</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>36</v>
-      </c>
-      <c r="N21" t="s">
-        <v>75</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D22">
+        <v>2222</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
-      </c>
-      <c r="K22" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K22">
+        <v>123</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>2222</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
-      </c>
-      <c r="K23" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K23">
+        <v>123</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>2222</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="K24">
+        <v>123</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N24" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>2222</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25">
+        <v>123</v>
+      </c>
+      <c r="L25" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" t="s">
+        <v>60</v>
+      </c>
+      <c r="N25" t="s">
         <v>77</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" t="s">
-        <v>72</v>
-      </c>
-      <c r="K25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>63</v>
-      </c>
-      <c r="N25" t="s">
-        <v>80</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>2222</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
-      </c>
-      <c r="K26" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K26">
+        <v>123</v>
       </c>
       <c r="L26" t="s">
         <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q26" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>2222</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
-      </c>
-      <c r="K27" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K27">
+        <v>123</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>2222</v>
+      </c>
+      <c r="F28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28">
+        <v>123</v>
+      </c>
+      <c r="L28" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" t="s">
+        <v>60</v>
+      </c>
+      <c r="N28" t="s">
         <v>81</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" t="s">
-        <v>72</v>
-      </c>
-      <c r="K28" t="s">
-        <v>35</v>
-      </c>
-      <c r="L28" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" t="s">
-        <v>63</v>
-      </c>
-      <c r="N28" t="s">
-        <v>84</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q28" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>2222</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
-      </c>
-      <c r="K29" t="s">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="K29">
+        <v>123</v>
       </c>
       <c r="L29" t="s">
         <v>21</v>
       </c>
       <c r="M29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N29" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D30">
+        <v>2222</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
-      </c>
-      <c r="K30" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K30">
+        <v>123</v>
       </c>
       <c r="L30" t="s">
         <v>21</v>
       </c>
       <c r="M30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N30" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D31">
+        <v>2222</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
-      </c>
-      <c r="K31" t="s">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="K31">
+        <v>123</v>
       </c>
       <c r="L31" t="s">
         <v>21</v>
       </c>
       <c r="M31" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q31" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>2222</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
-      </c>
-      <c r="K32" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K32">
+        <v>123</v>
       </c>
       <c r="L32" t="s">
         <v>21</v>
       </c>
       <c r="M32" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <v>2222</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K33" t="s">
-        <v>35</v>
+        <v>69</v>
+      </c>
+      <c r="K33">
+        <v>123</v>
       </c>
       <c r="L33" t="s">
         <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N33" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>218</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>2222</v>
+      </c>
+      <c r="F34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" t="s">
+        <v>69</v>
+      </c>
+      <c r="K34">
+        <v>123</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" t="s">
+        <v>63</v>
+      </c>
+      <c r="N34" t="s">
         <v>87</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" t="s">
-        <v>72</v>
-      </c>
-      <c r="K34" t="s">
-        <v>22</v>
-      </c>
-      <c r="L34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" t="s">
-        <v>66</v>
-      </c>
-      <c r="N34" t="s">
-        <v>90</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D35">
+        <v>2222</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
-      </c>
-      <c r="K35" t="s">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="K35">
+        <v>123</v>
       </c>
       <c r="L35" t="s">
         <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N35" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36">
+        <v>2222</v>
+      </c>
+      <c r="F36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" t="s">
+        <v>90</v>
+      </c>
+      <c r="K36">
+        <v>123</v>
+      </c>
+      <c r="L36" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" t="s">
+        <v>33</v>
+      </c>
+      <c r="N36" t="s">
         <v>91</v>
       </c>
-      <c r="Q35" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="O36">
+        <v>29</v>
+      </c>
+      <c r="P36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37">
+        <v>2222</v>
+      </c>
+      <c r="F37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37">
+        <v>123</v>
+      </c>
+      <c r="L37" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37" t="s">
         <v>93</v>
-      </c>
-      <c r="K36" t="s">
-        <v>35</v>
-      </c>
-      <c r="L36" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" t="s">
-        <v>36</v>
-      </c>
-      <c r="N36" t="s">
-        <v>94</v>
-      </c>
-      <c r="O36">
-        <v>29</v>
-      </c>
-      <c r="P36" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" t="s">
-        <v>93</v>
-      </c>
-      <c r="K37" t="s">
-        <v>35</v>
-      </c>
-      <c r="L37" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" t="s">
-        <v>43</v>
-      </c>
-      <c r="N37" t="s">
-        <v>96</v>
       </c>
       <c r="O37">
         <v>9</v>
       </c>
       <c r="P37" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q37" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>2222</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>93</v>
-      </c>
-      <c r="K38" t="s">
-        <v>22</v>
+        <v>90</v>
+      </c>
+      <c r="K38">
+        <v>123</v>
       </c>
       <c r="L38" t="s">
         <v>21</v>
       </c>
       <c r="M38" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38" t="s">
+        <v>95</v>
+      </c>
+      <c r="O38">
+        <v>29</v>
+      </c>
+      <c r="P38" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>218</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39">
+        <v>2222</v>
+      </c>
+      <c r="F39" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39" t="s">
+        <v>90</v>
+      </c>
+      <c r="K39">
+        <v>123</v>
+      </c>
+      <c r="L39" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" t="s">
         <v>43</v>
-      </c>
-      <c r="N38" t="s">
-        <v>98</v>
-      </c>
-      <c r="O38">
-        <v>29</v>
-      </c>
-      <c r="P38" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
-      </c>
-      <c r="H39" t="s">
-        <v>93</v>
-      </c>
-      <c r="K39" t="s">
-        <v>22</v>
-      </c>
-      <c r="L39" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" t="s">
-        <v>45</v>
-      </c>
-      <c r="N39" t="s">
-        <v>46</v>
       </c>
       <c r="O39">
         <v>9</v>
       </c>
       <c r="P39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q39" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D40">
+        <v>2222</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>93</v>
-      </c>
-      <c r="K40" t="s">
-        <v>22</v>
+        <v>90</v>
+      </c>
+      <c r="K40">
+        <v>123</v>
       </c>
       <c r="L40" t="s">
         <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O40">
         <v>29</v>
       </c>
       <c r="P40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D41">
+        <v>2222</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>93</v>
-      </c>
-      <c r="K41" t="s">
-        <v>22</v>
+        <v>90</v>
+      </c>
+      <c r="K41">
+        <v>123</v>
       </c>
       <c r="L41" t="s">
         <v>21</v>
       </c>
       <c r="M41" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O41">
         <v>9</v>
       </c>
       <c r="P41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q41" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D42">
+        <v>2222</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" t="s">
+        <v>90</v>
+      </c>
+      <c r="K42">
+        <v>123</v>
+      </c>
+      <c r="L42" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" t="s">
+        <v>60</v>
+      </c>
+      <c r="N42" t="s">
+        <v>99</v>
+      </c>
+      <c r="O42">
+        <v>29</v>
+      </c>
+      <c r="P42" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43">
+        <v>2222</v>
+      </c>
+      <c r="F43" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" t="s">
+        <v>90</v>
+      </c>
+      <c r="K43">
+        <v>123</v>
+      </c>
+      <c r="L43" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" t="s">
+        <v>63</v>
+      </c>
+      <c r="N43" t="s">
+        <v>100</v>
+      </c>
+      <c r="O43">
+        <v>29</v>
+      </c>
+      <c r="P43" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44">
+        <v>2222</v>
+      </c>
+      <c r="F44" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" t="s">
+        <v>90</v>
+      </c>
+      <c r="K44">
+        <v>123</v>
+      </c>
+      <c r="L44" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" t="s">
+        <v>101</v>
+      </c>
+      <c r="N44" t="s">
+        <v>102</v>
+      </c>
+      <c r="O44">
+        <v>29</v>
+      </c>
+      <c r="P44" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45">
+        <v>2222</v>
+      </c>
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" t="s">
+        <v>90</v>
+      </c>
+      <c r="K45">
+        <v>123</v>
+      </c>
+      <c r="L45" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" t="s">
+        <v>104</v>
+      </c>
+      <c r="N45" t="s">
+        <v>105</v>
+      </c>
+      <c r="O45">
+        <v>29</v>
+      </c>
+      <c r="P45" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>218</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46">
+        <v>2222</v>
+      </c>
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
+        <v>106</v>
+      </c>
+      <c r="K46">
+        <v>123</v>
+      </c>
+      <c r="L46" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" t="s">
         <v>33</v>
       </c>
-      <c r="H42" t="s">
-        <v>93</v>
-      </c>
-      <c r="K42" t="s">
-        <v>22</v>
-      </c>
-      <c r="L42" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" t="s">
-        <v>63</v>
-      </c>
-      <c r="N42" t="s">
-        <v>102</v>
-      </c>
-      <c r="O42">
-        <v>29</v>
-      </c>
-      <c r="P42" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" t="s">
-        <v>33</v>
-      </c>
-      <c r="H43" t="s">
-        <v>93</v>
-      </c>
-      <c r="K43" t="s">
-        <v>35</v>
-      </c>
-      <c r="L43" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" t="s">
-        <v>66</v>
-      </c>
-      <c r="N43" t="s">
-        <v>103</v>
-      </c>
-      <c r="O43">
-        <v>29</v>
-      </c>
-      <c r="P43" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" t="s">
-        <v>33</v>
-      </c>
-      <c r="H44" t="s">
-        <v>93</v>
-      </c>
-      <c r="K44" t="s">
-        <v>35</v>
-      </c>
-      <c r="L44" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N44" t="s">
-        <v>105</v>
-      </c>
-      <c r="O44">
-        <v>29</v>
-      </c>
-      <c r="P44" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" t="s">
-        <v>33</v>
-      </c>
-      <c r="H45" t="s">
-        <v>93</v>
-      </c>
-      <c r="K45" t="s">
-        <v>22</v>
-      </c>
-      <c r="L45" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" t="s">
+      <c r="N46" t="s">
         <v>107</v>
-      </c>
-      <c r="N45" t="s">
-        <v>108</v>
-      </c>
-      <c r="O45">
-        <v>29</v>
-      </c>
-      <c r="P45" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" t="s">
-        <v>33</v>
-      </c>
-      <c r="H46" t="s">
-        <v>109</v>
-      </c>
-      <c r="K46" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" t="s">
-        <v>36</v>
-      </c>
-      <c r="N46" t="s">
-        <v>110</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D47">
+        <v>2222</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H47" t="s">
+        <v>106</v>
+      </c>
+      <c r="K47">
+        <v>123</v>
+      </c>
+      <c r="L47" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" t="s">
+        <v>40</v>
+      </c>
+      <c r="N47" t="s">
         <v>109</v>
-      </c>
-      <c r="K47" t="s">
-        <v>22</v>
-      </c>
-      <c r="L47" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" t="s">
-        <v>43</v>
-      </c>
-      <c r="N47" t="s">
-        <v>112</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q47" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D48">
+        <v>2222</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>109</v>
-      </c>
-      <c r="K48" t="s">
-        <v>35</v>
+        <v>106</v>
+      </c>
+      <c r="K48">
+        <v>123</v>
       </c>
       <c r="L48" t="s">
         <v>21</v>
       </c>
       <c r="M48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N48" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>218</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49">
+        <v>2222</v>
+      </c>
+      <c r="F49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" t="s">
+        <v>112</v>
+      </c>
+      <c r="K49">
+        <v>123</v>
+      </c>
+      <c r="L49" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" t="s">
+        <v>33</v>
+      </c>
+      <c r="N49" t="s">
         <v>113</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" t="s">
-        <v>32</v>
-      </c>
-      <c r="G49" t="s">
-        <v>33</v>
-      </c>
-      <c r="H49" t="s">
-        <v>115</v>
-      </c>
-      <c r="K49" t="s">
-        <v>35</v>
-      </c>
-      <c r="L49" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" t="s">
-        <v>36</v>
-      </c>
-      <c r="N49" t="s">
-        <v>116</v>
       </c>
       <c r="O49">
         <v>13</v>
       </c>
       <c r="P49" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q49" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D50">
+        <v>2222</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
+        <v>112</v>
+      </c>
+      <c r="K50">
+        <v>123</v>
+      </c>
+      <c r="L50" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" t="s">
+        <v>40</v>
+      </c>
+      <c r="N50" t="s">
         <v>115</v>
-      </c>
-      <c r="K50" t="s">
-        <v>22</v>
-      </c>
-      <c r="L50" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" t="s">
-        <v>43</v>
-      </c>
-      <c r="N50" t="s">
-        <v>118</v>
       </c>
       <c r="O50">
         <v>13</v>
       </c>
       <c r="P50" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q50" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D51">
+        <v>2222</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>115</v>
-      </c>
-      <c r="K51" t="s">
-        <v>22</v>
+        <v>112</v>
+      </c>
+      <c r="K51">
+        <v>123</v>
       </c>
       <c r="L51" t="s">
         <v>21</v>
       </c>
       <c r="M51" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q51" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D52">
+        <v>2222</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>115</v>
-      </c>
-      <c r="K52" t="s">
-        <v>35</v>
+        <v>112</v>
+      </c>
+      <c r="K52">
+        <v>123</v>
       </c>
       <c r="L52" t="s">
         <v>21</v>
       </c>
       <c r="M52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N52" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O52">
         <v>13</v>
       </c>
       <c r="P52" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q52" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D53">
+        <v>2222</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>115</v>
-      </c>
-      <c r="K53" t="s">
-        <v>22</v>
+        <v>112</v>
+      </c>
+      <c r="K53">
+        <v>123</v>
       </c>
       <c r="L53" t="s">
         <v>21</v>
       </c>
       <c r="M53" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N53" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q53" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D54">
+        <v>2222</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>115</v>
-      </c>
-      <c r="K54" t="s">
-        <v>35</v>
+        <v>112</v>
+      </c>
+      <c r="K54">
+        <v>123</v>
       </c>
       <c r="L54" t="s">
         <v>21</v>
       </c>
       <c r="M54" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N54" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O54">
         <v>13</v>
       </c>
       <c r="P54" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q54" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D55">
+        <v>2222</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H55" t="s">
-        <v>115</v>
-      </c>
-      <c r="K55" t="s">
-        <v>35</v>
+        <v>112</v>
+      </c>
+      <c r="K55">
+        <v>123</v>
       </c>
       <c r="L55" t="s">
         <v>21</v>
       </c>
       <c r="M55" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N55" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q55" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D56">
+        <v>2222</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>115</v>
-      </c>
-      <c r="K56" t="s">
-        <v>35</v>
+        <v>112</v>
+      </c>
+      <c r="K56">
+        <v>123</v>
       </c>
       <c r="L56" t="s">
         <v>21</v>
       </c>
       <c r="M56" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N56" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O56">
         <v>13</v>
       </c>
       <c r="P56" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
-      </c>
-      <c r="D57" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D57">
+        <v>2222</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>115</v>
-      </c>
-      <c r="K57" t="s">
-        <v>22</v>
+        <v>112</v>
+      </c>
+      <c r="K57">
+        <v>123</v>
       </c>
       <c r="L57" t="s">
         <v>21</v>
       </c>
       <c r="M57" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N57" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O57">
         <v>13</v>
       </c>
       <c r="P57" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q57" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
-      </c>
-      <c r="D58" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D58">
+        <v>2222</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H58" t="s">
-        <v>115</v>
-      </c>
-      <c r="K58" t="s">
-        <v>35</v>
+        <v>112</v>
+      </c>
+      <c r="K58">
+        <v>123</v>
       </c>
       <c r="L58" t="s">
         <v>21</v>
       </c>
       <c r="M58" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N58" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O58">
         <v>13</v>
       </c>
       <c r="P58" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q58" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
-      </c>
-      <c r="D59" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D59">
+        <v>2222</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" t="s">
+        <v>126</v>
+      </c>
+      <c r="K59">
+        <v>123</v>
+      </c>
+      <c r="L59" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" t="s">
         <v>33</v>
       </c>
-      <c r="H59" t="s">
-        <v>129</v>
-      </c>
-      <c r="K59" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" t="s">
-        <v>36</v>
-      </c>
       <c r="N59" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O59">
         <v>15</v>
       </c>
       <c r="P59" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q59" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D60">
+        <v>2222</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" t="s">
+        <v>126</v>
+      </c>
+      <c r="K60">
+        <v>123</v>
+      </c>
+      <c r="L60" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" t="s">
         <v>33</v>
       </c>
-      <c r="H60" t="s">
+      <c r="N60" t="s">
         <v>129</v>
-      </c>
-      <c r="K60" t="s">
-        <v>22</v>
-      </c>
-      <c r="L60" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" t="s">
-        <v>36</v>
-      </c>
-      <c r="N60" t="s">
-        <v>132</v>
       </c>
       <c r="O60">
         <v>15</v>
       </c>
       <c r="P60" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q60" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D61">
+        <v>2222</v>
       </c>
       <c r="F61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H61" t="s">
-        <v>129</v>
-      </c>
-      <c r="K61" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K61">
+        <v>123</v>
       </c>
       <c r="L61" t="s">
         <v>21</v>
       </c>
       <c r="M61" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N61" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O61">
         <v>7</v>
       </c>
       <c r="P61" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q61" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
-      </c>
-      <c r="D62" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D62">
+        <v>2222</v>
       </c>
       <c r="F62" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>129</v>
-      </c>
-      <c r="K62" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K62">
+        <v>123</v>
       </c>
       <c r="L62" t="s">
         <v>21</v>
       </c>
       <c r="M62" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N62" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O62">
         <v>15</v>
       </c>
       <c r="P62" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q62" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D63">
+        <v>2222</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>129</v>
-      </c>
-      <c r="K63" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K63">
+        <v>123</v>
       </c>
       <c r="L63" t="s">
         <v>21</v>
       </c>
       <c r="M63" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N63" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q63" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D64">
+        <v>2222</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>129</v>
-      </c>
-      <c r="K64" t="s">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="K64">
+        <v>123</v>
       </c>
       <c r="L64" t="s">
         <v>21</v>
       </c>
       <c r="M64" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N64" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O64">
         <v>7</v>
       </c>
       <c r="P64" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q64" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D65">
+        <v>2222</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>129</v>
-      </c>
-      <c r="K65" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K65">
+        <v>123</v>
       </c>
       <c r="L65" t="s">
         <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N65" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O65">
         <v>15</v>
       </c>
       <c r="P65" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q65" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D66">
+        <v>2222</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>129</v>
-      </c>
-      <c r="K66" t="s">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="K66">
+        <v>123</v>
       </c>
       <c r="L66" t="s">
         <v>21</v>
       </c>
       <c r="M66" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N66" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O66">
         <v>15</v>
       </c>
       <c r="P66" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q66" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D67">
+        <v>2222</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>129</v>
-      </c>
-      <c r="K67" t="s">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="K67">
+        <v>123</v>
       </c>
       <c r="L67" t="s">
         <v>21</v>
       </c>
       <c r="M67" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N67" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q67" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
-      </c>
-      <c r="D68" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D68">
+        <v>2222</v>
       </c>
       <c r="F68" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>129</v>
-      </c>
-      <c r="K68" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K68">
+        <v>123</v>
       </c>
       <c r="L68" t="s">
         <v>21</v>
       </c>
       <c r="M68" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N68" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O68">
         <v>7</v>
       </c>
       <c r="P68" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q68" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
-      </c>
-      <c r="D69" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D69">
+        <v>2222</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>129</v>
-      </c>
-      <c r="K69" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K69">
+        <v>123</v>
       </c>
       <c r="L69" t="s">
         <v>21</v>
       </c>
       <c r="M69" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N69" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O69">
         <v>15</v>
       </c>
       <c r="P69" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q69" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
-      </c>
-      <c r="D70" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D70">
+        <v>2222</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>129</v>
-      </c>
-      <c r="K70" t="s">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="K70">
+        <v>123</v>
       </c>
       <c r="L70" t="s">
         <v>21</v>
       </c>
       <c r="M70" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N70" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q70" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
-      </c>
-      <c r="D71" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D71">
+        <v>2222</v>
       </c>
       <c r="F71" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>129</v>
-      </c>
-      <c r="K71" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K71">
+        <v>123</v>
       </c>
       <c r="L71" t="s">
         <v>21</v>
       </c>
       <c r="M71" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N71" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q71" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D72">
+        <v>2222</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>129</v>
-      </c>
-      <c r="K72" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K72">
+        <v>123</v>
       </c>
       <c r="L72" t="s">
         <v>21</v>
       </c>
       <c r="M72" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N72" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O72">
         <v>15</v>
       </c>
       <c r="P72" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q72" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
-      </c>
-      <c r="D73" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D73">
+        <v>2222</v>
       </c>
       <c r="F73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>129</v>
-      </c>
-      <c r="K73" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="K73">
+        <v>123</v>
       </c>
       <c r="L73" t="s">
         <v>21</v>
       </c>
       <c r="M73" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N73" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O73">
         <v>15</v>
       </c>
       <c r="P73" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q73" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
-      </c>
-      <c r="D74" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D74">
+        <v>2222</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>129</v>
-      </c>
-      <c r="K74" t="s">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="K74">
+        <v>123</v>
       </c>
       <c r="L74" t="s">
         <v>21</v>
       </c>
       <c r="M74" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N74" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O74">
         <v>15</v>
       </c>
       <c r="P74" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>218</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75">
+        <v>2222</v>
+      </c>
+      <c r="F75" t="s">
+        <v>30</v>
+      </c>
+      <c r="G75" t="s">
+        <v>31</v>
+      </c>
+      <c r="H75" t="s">
+        <v>145</v>
+      </c>
+      <c r="K75">
+        <v>123</v>
+      </c>
+      <c r="L75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" t="s">
+        <v>33</v>
+      </c>
+      <c r="N75" t="s">
         <v>146</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>29</v>
-      </c>
-      <c r="B75" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" t="s">
-        <v>31</v>
-      </c>
-      <c r="F75" t="s">
-        <v>32</v>
-      </c>
-      <c r="G75" t="s">
-        <v>33</v>
-      </c>
-      <c r="H75" t="s">
-        <v>148</v>
-      </c>
-      <c r="K75" t="s">
-        <v>22</v>
-      </c>
-      <c r="L75" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" t="s">
-        <v>36</v>
-      </c>
-      <c r="N75" t="s">
-        <v>149</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q75" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D76">
+        <v>2222</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76" t="s">
+        <v>145</v>
+      </c>
+      <c r="K76">
+        <v>123</v>
+      </c>
+      <c r="L76" t="s">
+        <v>21</v>
+      </c>
+      <c r="M76" t="s">
         <v>33</v>
       </c>
-      <c r="H76" t="s">
-        <v>148</v>
-      </c>
-      <c r="K76" t="s">
-        <v>22</v>
-      </c>
-      <c r="L76" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" t="s">
-        <v>36</v>
-      </c>
       <c r="N76" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q76" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
-      </c>
-      <c r="D77" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D77">
+        <v>2222</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" t="s">
+        <v>145</v>
+      </c>
+      <c r="K77">
+        <v>123</v>
+      </c>
+      <c r="L77" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" t="s">
         <v>33</v>
       </c>
-      <c r="H77" t="s">
-        <v>148</v>
-      </c>
-      <c r="K77" t="s">
-        <v>35</v>
-      </c>
-      <c r="L77" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" t="s">
-        <v>36</v>
-      </c>
       <c r="N77" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q77" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D78">
+        <v>2222</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G78" t="s">
+        <v>31</v>
+      </c>
+      <c r="H78" t="s">
+        <v>145</v>
+      </c>
+      <c r="K78">
+        <v>123</v>
+      </c>
+      <c r="L78" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" t="s">
         <v>33</v>
       </c>
-      <c r="H78" t="s">
-        <v>148</v>
-      </c>
-      <c r="K78" t="s">
-        <v>22</v>
-      </c>
-      <c r="L78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" t="s">
-        <v>36</v>
-      </c>
       <c r="N78" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q78" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D79">
+        <v>2222</v>
       </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H79" t="s">
-        <v>148</v>
-      </c>
-      <c r="K79" t="s">
-        <v>35</v>
+        <v>145</v>
+      </c>
+      <c r="K79">
+        <v>123</v>
       </c>
       <c r="L79" t="s">
         <v>21</v>
       </c>
       <c r="M79" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N79" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q79" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
-      </c>
-      <c r="D80" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D80">
+        <v>2222</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H80" t="s">
-        <v>148</v>
-      </c>
-      <c r="K80" t="s">
-        <v>22</v>
+        <v>145</v>
+      </c>
+      <c r="K80">
+        <v>123</v>
       </c>
       <c r="L80" t="s">
         <v>21</v>
       </c>
       <c r="M80" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N80" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
-      </c>
-      <c r="D81" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D81">
+        <v>2222</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H81" t="s">
-        <v>148</v>
-      </c>
-      <c r="K81" t="s">
-        <v>22</v>
+        <v>145</v>
+      </c>
+      <c r="K81">
+        <v>123</v>
       </c>
       <c r="L81" t="s">
         <v>21</v>
       </c>
       <c r="M81" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N81" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q81" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
-      </c>
-      <c r="D82" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D82">
+        <v>2222</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H82" t="s">
-        <v>148</v>
-      </c>
-      <c r="K82" t="s">
-        <v>22</v>
+        <v>145</v>
+      </c>
+      <c r="K82">
+        <v>123</v>
       </c>
       <c r="L82" t="s">
         <v>21</v>
       </c>
       <c r="M82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N82" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q82" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
-      </c>
-      <c r="D83" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D83">
+        <v>2222</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H83" t="s">
-        <v>148</v>
-      </c>
-      <c r="K83" t="s">
-        <v>22</v>
+        <v>145</v>
+      </c>
+      <c r="K83">
+        <v>123</v>
       </c>
       <c r="L83" t="s">
         <v>21</v>
       </c>
       <c r="M83" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N83" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q83" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
-      </c>
-      <c r="D84" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D84">
+        <v>2222</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H84" t="s">
-        <v>148</v>
-      </c>
-      <c r="K84" t="s">
-        <v>35</v>
+        <v>145</v>
+      </c>
+      <c r="K84">
+        <v>123</v>
       </c>
       <c r="L84" t="s">
         <v>21</v>
       </c>
       <c r="M84" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N84" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q84" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
-      </c>
-      <c r="D85" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D85">
+        <v>2222</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H85" t="s">
-        <v>148</v>
-      </c>
-      <c r="K85" t="s">
-        <v>35</v>
+        <v>145</v>
+      </c>
+      <c r="K85">
+        <v>123</v>
       </c>
       <c r="L85" t="s">
         <v>21</v>
       </c>
       <c r="M85" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N85" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q85" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
-      </c>
-      <c r="D86" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D86">
+        <v>2222</v>
       </c>
       <c r="F86" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H86" t="s">
-        <v>148</v>
-      </c>
-      <c r="K86" t="s">
-        <v>22</v>
+        <v>145</v>
+      </c>
+      <c r="K86">
+        <v>123</v>
       </c>
       <c r="L86" t="s">
         <v>21</v>
       </c>
       <c r="M86" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N86" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>218</v>
+      </c>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87">
+        <v>2222</v>
+      </c>
+      <c r="F87" t="s">
+        <v>30</v>
+      </c>
+      <c r="G87" t="s">
+        <v>31</v>
+      </c>
+      <c r="H87" t="s">
         <v>162</v>
       </c>
-      <c r="Q86" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>29</v>
-      </c>
-      <c r="B87" t="s">
-        <v>30</v>
-      </c>
-      <c r="D87" t="s">
-        <v>31</v>
-      </c>
-      <c r="F87" t="s">
-        <v>32</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="K87">
+        <v>123</v>
+      </c>
+      <c r="L87" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" t="s">
         <v>33</v>
       </c>
-      <c r="H87" t="s">
-        <v>165</v>
-      </c>
-      <c r="K87" t="s">
-        <v>35</v>
-      </c>
-      <c r="L87" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" t="s">
-        <v>36</v>
-      </c>
       <c r="N87" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O87">
         <v>40</v>
       </c>
       <c r="P87" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q87" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
-      </c>
-      <c r="D88" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D88">
+        <v>2222</v>
       </c>
       <c r="F88" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G88" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H88" t="s">
+        <v>162</v>
+      </c>
+      <c r="K88">
+        <v>123</v>
+      </c>
+      <c r="L88" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" t="s">
+        <v>40</v>
+      </c>
+      <c r="N88" t="s">
         <v>165</v>
-      </c>
-      <c r="K88" t="s">
-        <v>22</v>
-      </c>
-      <c r="L88" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" t="s">
-        <v>43</v>
-      </c>
-      <c r="N88" t="s">
-        <v>168</v>
       </c>
       <c r="O88">
         <v>40</v>
       </c>
       <c r="P88" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q88" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
-      </c>
-      <c r="D89" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D89">
+        <v>2222</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H89" t="s">
-        <v>165</v>
-      </c>
-      <c r="K89" t="s">
-        <v>22</v>
+        <v>162</v>
+      </c>
+      <c r="K89">
+        <v>123</v>
       </c>
       <c r="L89" t="s">
         <v>21</v>
       </c>
       <c r="M89" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N89" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q89" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D90">
+        <v>2222</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G90" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H90" t="s">
-        <v>165</v>
-      </c>
-      <c r="K90" t="s">
-        <v>35</v>
+        <v>162</v>
+      </c>
+      <c r="K90">
+        <v>123</v>
       </c>
       <c r="L90" t="s">
         <v>21</v>
       </c>
       <c r="M90" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N90" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O90">
         <v>12</v>
       </c>
       <c r="P90" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Q90" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
-      </c>
-      <c r="D91" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D91">
+        <v>2222</v>
       </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G91" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H91" t="s">
-        <v>165</v>
-      </c>
-      <c r="K91" t="s">
-        <v>35</v>
+        <v>162</v>
+      </c>
+      <c r="K91">
+        <v>123</v>
       </c>
       <c r="L91" t="s">
         <v>21</v>
       </c>
       <c r="M91" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N91" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O91">
         <v>40</v>
       </c>
       <c r="P91" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q91" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
-      </c>
-      <c r="D92" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D92">
+        <v>2222</v>
       </c>
       <c r="F92" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G92" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H92" t="s">
-        <v>165</v>
-      </c>
-      <c r="K92" t="s">
-        <v>35</v>
+        <v>162</v>
+      </c>
+      <c r="K92">
+        <v>123</v>
       </c>
       <c r="L92" t="s">
         <v>21</v>
       </c>
       <c r="M92" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N92" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="O92">
         <v>12</v>
       </c>
       <c r="P92" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q92" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
-      </c>
-      <c r="D93" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D93">
+        <v>2222</v>
       </c>
       <c r="F93" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G93" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H93" t="s">
-        <v>165</v>
-      </c>
-      <c r="K93" t="s">
-        <v>22</v>
+        <v>162</v>
+      </c>
+      <c r="K93">
+        <v>123</v>
       </c>
       <c r="L93" t="s">
         <v>21</v>
       </c>
       <c r="M93" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N93" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O93">
         <v>40</v>
       </c>
       <c r="P93" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q93" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
-      </c>
-      <c r="D94" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D94">
+        <v>2222</v>
       </c>
       <c r="F94" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G94" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H94" t="s">
-        <v>165</v>
-      </c>
-      <c r="K94" t="s">
-        <v>22</v>
+        <v>162</v>
+      </c>
+      <c r="K94">
+        <v>123</v>
       </c>
       <c r="L94" t="s">
         <v>21</v>
       </c>
       <c r="M94" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N94" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O94">
         <v>12</v>
       </c>
       <c r="P94" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q94" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
-      </c>
-      <c r="D95" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D95">
+        <v>2222</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G95" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H95" t="s">
-        <v>165</v>
-      </c>
-      <c r="K95" t="s">
-        <v>35</v>
+        <v>162</v>
+      </c>
+      <c r="K95">
+        <v>123</v>
       </c>
       <c r="L95" t="s">
         <v>21</v>
       </c>
       <c r="M95" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N95" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="O95">
         <v>40</v>
       </c>
       <c r="P95" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q95" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
-      </c>
-      <c r="D96" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D96">
+        <v>2222</v>
       </c>
       <c r="F96" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G96" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H96" t="s">
-        <v>165</v>
-      </c>
-      <c r="K96" t="s">
-        <v>35</v>
+        <v>162</v>
+      </c>
+      <c r="K96">
+        <v>123</v>
       </c>
       <c r="L96" t="s">
         <v>21</v>
       </c>
       <c r="M96" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N96" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="O96">
         <v>40</v>
       </c>
       <c r="P96" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q96" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D97">
+        <v>2222</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G97" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H97" t="s">
-        <v>165</v>
-      </c>
-      <c r="K97" t="s">
-        <v>22</v>
+        <v>162</v>
+      </c>
+      <c r="K97">
+        <v>123</v>
       </c>
       <c r="L97" t="s">
         <v>21</v>
       </c>
       <c r="M97" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N97" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O97">
         <v>40</v>
       </c>
       <c r="P97" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q97" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
-      </c>
-      <c r="D98" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D98">
+        <v>2222</v>
       </c>
       <c r="F98" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G98" t="s">
+        <v>31</v>
+      </c>
+      <c r="H98" t="s">
+        <v>182</v>
+      </c>
+      <c r="K98">
+        <v>123</v>
+      </c>
+      <c r="L98" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" t="s">
         <v>33</v>
       </c>
-      <c r="H98" t="s">
-        <v>185</v>
-      </c>
-      <c r="K98" t="s">
-        <v>35</v>
-      </c>
-      <c r="L98" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" t="s">
-        <v>36</v>
-      </c>
       <c r="N98" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q98" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
-      </c>
-      <c r="D99" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D99">
+        <v>2222</v>
       </c>
       <c r="F99" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G99" t="s">
+        <v>31</v>
+      </c>
+      <c r="H99" t="s">
+        <v>182</v>
+      </c>
+      <c r="K99">
+        <v>123</v>
+      </c>
+      <c r="L99" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" t="s">
         <v>33</v>
       </c>
-      <c r="H99" t="s">
-        <v>185</v>
-      </c>
-      <c r="K99" t="s">
-        <v>22</v>
-      </c>
-      <c r="L99" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" t="s">
-        <v>36</v>
-      </c>
       <c r="N99" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q99" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B100" t="s">
-        <v>30</v>
-      </c>
-      <c r="D100" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D100">
+        <v>2222</v>
       </c>
       <c r="F100" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G100" t="s">
+        <v>31</v>
+      </c>
+      <c r="H100" t="s">
+        <v>182</v>
+      </c>
+      <c r="K100">
+        <v>123</v>
+      </c>
+      <c r="L100" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" t="s">
         <v>33</v>
       </c>
-      <c r="H100" t="s">
-        <v>185</v>
-      </c>
-      <c r="K100" t="s">
-        <v>22</v>
-      </c>
-      <c r="L100" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" t="s">
-        <v>36</v>
-      </c>
       <c r="N100" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O100">
         <v>6</v>
       </c>
       <c r="P100" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q100" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
-      </c>
-      <c r="D101" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D101">
+        <v>2222</v>
       </c>
       <c r="F101" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G101" t="s">
+        <v>31</v>
+      </c>
+      <c r="H101" t="s">
+        <v>182</v>
+      </c>
+      <c r="K101">
+        <v>123</v>
+      </c>
+      <c r="L101" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" t="s">
         <v>33</v>
       </c>
-      <c r="H101" t="s">
-        <v>185</v>
-      </c>
-      <c r="K101" t="s">
-        <v>35</v>
-      </c>
-      <c r="L101" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" t="s">
-        <v>36</v>
-      </c>
       <c r="N101" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O101">
         <v>0</v>
       </c>
       <c r="P101" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q101" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B102" t="s">
-        <v>30</v>
-      </c>
-      <c r="D102" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D102">
+        <v>2222</v>
       </c>
       <c r="F102" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G102" t="s">
+        <v>31</v>
+      </c>
+      <c r="H102" t="s">
+        <v>182</v>
+      </c>
+      <c r="K102">
+        <v>123</v>
+      </c>
+      <c r="L102" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" t="s">
         <v>33</v>
       </c>
-      <c r="H102" t="s">
-        <v>185</v>
-      </c>
-      <c r="K102" t="s">
-        <v>22</v>
-      </c>
-      <c r="L102" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" t="s">
-        <v>36</v>
-      </c>
       <c r="N102" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O102">
         <v>12</v>
       </c>
       <c r="P102" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q102" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>30</v>
-      </c>
-      <c r="D103" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D103">
+        <v>2222</v>
       </c>
       <c r="F103" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G103" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H103" t="s">
-        <v>185</v>
-      </c>
-      <c r="K103" t="s">
-        <v>22</v>
+        <v>182</v>
+      </c>
+      <c r="K103">
+        <v>123</v>
       </c>
       <c r="L103" t="s">
         <v>21</v>
       </c>
       <c r="M103" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N103" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O103">
         <v>0</v>
       </c>
       <c r="P103" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>218</v>
+      </c>
+      <c r="B104" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104">
+        <v>2222</v>
+      </c>
+      <c r="F104" t="s">
+        <v>30</v>
+      </c>
+      <c r="G104" t="s">
+        <v>31</v>
+      </c>
+      <c r="H104" t="s">
+        <v>182</v>
+      </c>
+      <c r="K104">
+        <v>123</v>
+      </c>
+      <c r="L104" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" t="s">
+        <v>40</v>
+      </c>
+      <c r="N104" t="s">
         <v>189</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>29</v>
-      </c>
-      <c r="B104" t="s">
-        <v>30</v>
-      </c>
-      <c r="D104" t="s">
-        <v>31</v>
-      </c>
-      <c r="F104" t="s">
-        <v>32</v>
-      </c>
-      <c r="G104" t="s">
-        <v>33</v>
-      </c>
-      <c r="H104" t="s">
-        <v>185</v>
-      </c>
-      <c r="K104" t="s">
-        <v>22</v>
-      </c>
-      <c r="L104" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" t="s">
-        <v>43</v>
-      </c>
-      <c r="N104" t="s">
-        <v>192</v>
       </c>
       <c r="O104">
         <v>0</v>
       </c>
       <c r="P104" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q104" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
-        <v>30</v>
-      </c>
-      <c r="D105" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D105">
+        <v>2222</v>
       </c>
       <c r="F105" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G105" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H105" t="s">
-        <v>185</v>
-      </c>
-      <c r="K105" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K105">
+        <v>123</v>
       </c>
       <c r="L105" t="s">
         <v>21</v>
       </c>
       <c r="M105" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N105" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O105">
         <v>0</v>
       </c>
       <c r="P105" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q105" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
-      </c>
-      <c r="D106" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D106">
+        <v>2222</v>
       </c>
       <c r="F106" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G106" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H106" t="s">
-        <v>185</v>
-      </c>
-      <c r="K106" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K106">
+        <v>123</v>
       </c>
       <c r="L106" t="s">
         <v>21</v>
       </c>
       <c r="M106" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N106" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O106">
         <v>0</v>
       </c>
       <c r="P106" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q106" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
-      </c>
-      <c r="D107" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D107">
+        <v>2222</v>
       </c>
       <c r="F107" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G107" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H107" t="s">
-        <v>185</v>
-      </c>
-      <c r="K107" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K107">
+        <v>123</v>
       </c>
       <c r="L107" t="s">
         <v>21</v>
       </c>
       <c r="M107" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N107" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O107">
         <v>12</v>
       </c>
       <c r="P107" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q107" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
-      </c>
-      <c r="D108" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D108">
+        <v>2222</v>
       </c>
       <c r="F108" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G108" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H108" t="s">
-        <v>185</v>
-      </c>
-      <c r="K108" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K108">
+        <v>123</v>
       </c>
       <c r="L108" t="s">
         <v>21</v>
       </c>
       <c r="M108" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N108" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O108">
         <v>6</v>
       </c>
       <c r="P108" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q108" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B109" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D109">
+        <v>2222</v>
       </c>
       <c r="F109" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G109" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H109" t="s">
-        <v>185</v>
-      </c>
-      <c r="K109" t="s">
-        <v>22</v>
+        <v>182</v>
+      </c>
+      <c r="K109">
+        <v>123</v>
       </c>
       <c r="L109" t="s">
         <v>21</v>
       </c>
       <c r="M109" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N109" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O109">
         <v>12</v>
       </c>
       <c r="P109" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q109" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B110" t="s">
-        <v>30</v>
-      </c>
-      <c r="D110" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D110">
+        <v>2222</v>
       </c>
       <c r="F110" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G110" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H110" t="s">
-        <v>185</v>
-      </c>
-      <c r="K110" t="s">
-        <v>22</v>
+        <v>182</v>
+      </c>
+      <c r="K110">
+        <v>123</v>
       </c>
       <c r="L110" t="s">
         <v>21</v>
       </c>
       <c r="M110" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N110" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O110">
         <v>12</v>
       </c>
       <c r="P110" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q110" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B111" t="s">
-        <v>30</v>
-      </c>
-      <c r="D111" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D111">
+        <v>2222</v>
       </c>
       <c r="F111" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G111" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H111" t="s">
-        <v>185</v>
-      </c>
-      <c r="K111" t="s">
-        <v>22</v>
+        <v>182</v>
+      </c>
+      <c r="K111">
+        <v>123</v>
       </c>
       <c r="L111" t="s">
         <v>21</v>
       </c>
       <c r="M111" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N111" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O111">
         <v>12</v>
       </c>
       <c r="P111" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q111" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
-      </c>
-      <c r="D112" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D112">
+        <v>2222</v>
       </c>
       <c r="F112" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G112" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H112" t="s">
-        <v>185</v>
-      </c>
-      <c r="K112" t="s">
-        <v>22</v>
+        <v>182</v>
+      </c>
+      <c r="K112">
+        <v>123</v>
       </c>
       <c r="L112" t="s">
         <v>21</v>
       </c>
       <c r="M112" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N112" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O112">
         <v>12</v>
       </c>
       <c r="P112" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q112" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
-      </c>
-      <c r="D113" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D113">
+        <v>2222</v>
       </c>
       <c r="F113" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G113" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H113" t="s">
-        <v>185</v>
-      </c>
-      <c r="K113" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K113">
+        <v>123</v>
       </c>
       <c r="L113" t="s">
         <v>21</v>
       </c>
       <c r="M113" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N113" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O113">
         <v>6</v>
       </c>
       <c r="P113" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q113" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
-      </c>
-      <c r="D114" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D114">
+        <v>2222</v>
       </c>
       <c r="F114" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G114" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H114" t="s">
-        <v>185</v>
-      </c>
-      <c r="K114" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K114">
+        <v>123</v>
       </c>
       <c r="L114" t="s">
         <v>21</v>
       </c>
       <c r="M114" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N114" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="O114">
         <v>12</v>
       </c>
       <c r="P114" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q114" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
-      </c>
-      <c r="D115" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D115">
+        <v>2222</v>
       </c>
       <c r="F115" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G115" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H115" t="s">
-        <v>185</v>
-      </c>
-      <c r="K115" t="s">
-        <v>22</v>
+        <v>182</v>
+      </c>
+      <c r="K115">
+        <v>123</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>
       </c>
       <c r="M115" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N115" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O115">
         <v>12</v>
       </c>
       <c r="P115" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q115" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
-      </c>
-      <c r="D116" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D116">
+        <v>2222</v>
       </c>
       <c r="F116" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G116" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H116" t="s">
-        <v>185</v>
-      </c>
-      <c r="K116" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="K116">
+        <v>123</v>
       </c>
       <c r="L116" t="s">
         <v>21</v>
       </c>
       <c r="M116" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N116" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="O116">
         <v>12</v>
       </c>
       <c r="P116" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q116" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
-      </c>
-      <c r="D117" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D117">
+        <v>2222</v>
       </c>
       <c r="F117" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G117" t="s">
+        <v>31</v>
+      </c>
+      <c r="H117" t="s">
+        <v>201</v>
+      </c>
+      <c r="K117">
+        <v>123</v>
+      </c>
+      <c r="L117" t="s">
+        <v>21</v>
+      </c>
+      <c r="M117" t="s">
         <v>33</v>
       </c>
-      <c r="H117" t="s">
-        <v>204</v>
-      </c>
-      <c r="K117" t="s">
-        <v>35</v>
-      </c>
-      <c r="L117" t="s">
-        <v>21</v>
-      </c>
-      <c r="M117" t="s">
-        <v>36</v>
-      </c>
       <c r="N117" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O117">
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q117" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
-      </c>
-      <c r="D118" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D118">
+        <v>2222</v>
       </c>
       <c r="F118" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G118" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H118" t="s">
         <v>25</v>
       </c>
-      <c r="K118" t="s">
-        <v>22</v>
+      <c r="K118">
+        <v>123</v>
       </c>
       <c r="L118" t="s">
         <v>21</v>
       </c>
       <c r="M118" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N118" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O118">
         <v>28</v>
@@ -6425,77 +6415,77 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
-      </c>
-      <c r="D119" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D119">
+        <v>2222</v>
       </c>
       <c r="F119" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G119" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H119" t="s">
         <v>25</v>
       </c>
-      <c r="K119" t="s">
-        <v>35</v>
+      <c r="K119">
+        <v>123</v>
       </c>
       <c r="L119" t="s">
         <v>21</v>
       </c>
       <c r="M119" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N119" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="O119">
         <v>28</v>
       </c>
       <c r="P119" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q119" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
-      </c>
-      <c r="D120" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D120">
+        <v>2222</v>
       </c>
       <c r="F120" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G120" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H120" t="s">
         <v>25</v>
       </c>
-      <c r="K120" t="s">
-        <v>35</v>
+      <c r="K120">
+        <v>123</v>
       </c>
       <c r="L120" t="s">
         <v>21</v>
       </c>
       <c r="M120" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N120" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O120">
         <v>28</v>
@@ -6507,36 +6497,36 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
-      </c>
-      <c r="D121" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D121">
+        <v>2222</v>
       </c>
       <c r="F121" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G121" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H121" t="s">
         <v>25</v>
       </c>
-      <c r="K121" t="s">
-        <v>35</v>
+      <c r="K121">
+        <v>123</v>
       </c>
       <c r="L121" t="s">
         <v>21</v>
       </c>
       <c r="M121" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N121" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O121">
         <v>28</v>
@@ -6548,36 +6538,36 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B122" t="s">
-        <v>30</v>
-      </c>
-      <c r="D122" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D122">
+        <v>2222</v>
       </c>
       <c r="F122" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G122" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H122" t="s">
         <v>25</v>
       </c>
-      <c r="K122" t="s">
-        <v>22</v>
+      <c r="K122">
+        <v>123</v>
       </c>
       <c r="L122" t="s">
         <v>21</v>
       </c>
       <c r="M122" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N122" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O122">
         <v>28</v>
@@ -6589,77 +6579,77 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
-      </c>
-      <c r="D123" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D123">
+        <v>2222</v>
       </c>
       <c r="F123" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G123" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H123" t="s">
         <v>25</v>
       </c>
-      <c r="K123" t="s">
-        <v>22</v>
+      <c r="K123">
+        <v>123</v>
       </c>
       <c r="L123" t="s">
         <v>21</v>
       </c>
       <c r="M123" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N123" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O123">
         <v>28</v>
       </c>
       <c r="P123" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q123" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B124" t="s">
-        <v>30</v>
-      </c>
-      <c r="D124" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D124">
+        <v>2222</v>
       </c>
       <c r="F124" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G124" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H124" t="s">
         <v>25</v>
       </c>
-      <c r="K124" t="s">
-        <v>35</v>
+      <c r="K124">
+        <v>123</v>
       </c>
       <c r="L124" t="s">
         <v>21</v>
       </c>
       <c r="M124" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N124" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O124">
         <v>28</v>
@@ -6671,159 +6661,159 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
-      </c>
-      <c r="D125" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D125">
+        <v>2222</v>
       </c>
       <c r="F125" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G125" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H125" t="s">
         <v>25</v>
       </c>
-      <c r="K125" t="s">
-        <v>22</v>
+      <c r="K125">
+        <v>123</v>
       </c>
       <c r="L125" t="s">
         <v>21</v>
       </c>
       <c r="M125" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N125" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O125">
         <v>28</v>
       </c>
       <c r="P125" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q125" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
-      </c>
-      <c r="D126" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D126">
+        <v>2222</v>
       </c>
       <c r="F126" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G126" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H126" t="s">
         <v>25</v>
       </c>
-      <c r="K126" t="s">
-        <v>35</v>
+      <c r="K126">
+        <v>123</v>
       </c>
       <c r="L126" t="s">
         <v>21</v>
       </c>
       <c r="M126" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N126" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O126">
         <v>28</v>
       </c>
       <c r="P126" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q126" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
-      </c>
-      <c r="D127" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D127">
+        <v>2222</v>
       </c>
       <c r="F127" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G127" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H127" t="s">
         <v>25</v>
       </c>
-      <c r="K127" t="s">
-        <v>35</v>
+      <c r="K127">
+        <v>123</v>
       </c>
       <c r="L127" t="s">
         <v>21</v>
       </c>
       <c r="M127" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N127" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O127">
         <v>28</v>
       </c>
       <c r="P127" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q127" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
-      </c>
-      <c r="D128" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D128">
+        <v>2222</v>
       </c>
       <c r="F128" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H128" t="s">
         <v>25</v>
       </c>
-      <c r="K128" t="s">
-        <v>22</v>
+      <c r="K128">
+        <v>123</v>
       </c>
       <c r="L128" t="s">
         <v>21</v>
       </c>
       <c r="M128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N128" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O128">
         <v>28</v>
@@ -6835,165 +6825,165 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B129" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D129">
+        <v>2222</v>
       </c>
       <c r="F129" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G129" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H129" t="s">
         <v>25</v>
       </c>
-      <c r="K129" t="s">
-        <v>22</v>
+      <c r="K129">
+        <v>123</v>
       </c>
       <c r="L129" t="s">
         <v>21</v>
       </c>
       <c r="M129" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N129" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O129">
         <v>28</v>
       </c>
       <c r="P129" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q129" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B130" t="s">
-        <v>30</v>
-      </c>
-      <c r="D130" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D130">
+        <v>2222</v>
       </c>
       <c r="F130" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G130" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H130" t="s">
-        <v>218</v>
-      </c>
-      <c r="K130" t="s">
-        <v>22</v>
+        <v>215</v>
+      </c>
+      <c r="K130">
+        <v>123</v>
       </c>
       <c r="L130" t="s">
         <v>21</v>
       </c>
       <c r="M130" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N130" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O130">
         <v>8</v>
       </c>
       <c r="P130" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q130" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B131" t="s">
-        <v>30</v>
-      </c>
-      <c r="D131" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D131">
+        <v>2222</v>
       </c>
       <c r="F131" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H131" t="s">
-        <v>218</v>
-      </c>
-      <c r="K131" t="s">
-        <v>35</v>
+        <v>215</v>
+      </c>
+      <c r="K131">
+        <v>123</v>
       </c>
       <c r="L131" t="s">
         <v>21</v>
       </c>
       <c r="M131" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N131" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O131">
         <v>8</v>
       </c>
       <c r="P131" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q131" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="B132" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="D132">
+        <v>2222</v>
       </c>
       <c r="F132" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G132" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H132" t="s">
-        <v>218</v>
-      </c>
-      <c r="K132" t="s">
-        <v>35</v>
+        <v>215</v>
+      </c>
+      <c r="K132">
+        <v>123</v>
       </c>
       <c r="L132" t="s">
         <v>21</v>
       </c>
       <c r="M132" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N132" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O132">
         <v>8</v>
       </c>
       <c r="P132" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q132" t="s">
         <v>18</v>
@@ -7014,22 +7004,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" customWidth="1"/>
-    <col min="14" max="14" width="15.7265625" customWidth="1"/>
-    <col min="15" max="15" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.1796875" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
@@ -7050,7 +7040,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -7104,7 +7094,7 @@
       </c>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -7159,12 +7149,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a6a5fbd9-6557-41a9-9308-734b6878f3b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7401,17 +7390,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a6a5fbd9-6557-41a9-9308-734b6878f3b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781FBCB2-A824-4C1F-8939-2D068C9DF0BB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25DAB8A5-3A50-4C51-B07C-7E3995CE23F8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a6a5fbd9-6557-41a9-9308-734b6878f3b0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="e72a6f31-1b45-4752-a7a1-8716ea0243ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7436,18 +7435,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25DAB8A5-3A50-4C51-B07C-7E3995CE23F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781FBCB2-A824-4C1F-8939-2D068C9DF0BB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="a6a5fbd9-6557-41a9-9308-734b6878f3b0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="e72a6f31-1b45-4752-a7a1-8716ea0243ea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
